--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_310_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_310_R31.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2031</v>
+        <v>4.2545</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5113</v>
+        <v>1.8364</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6918</v>
+        <v>2.4181</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0709</v>
+        <v>0.8113</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7033</v>
+        <v>0.1788</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6323</v>
+        <v>0.6325</v>
       </c>
       <c r="J2" t="n">
-        <v>0.182</v>
+        <v>2.5526</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9683</v>
+        <v>2.1244</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7863</v>
+        <v>0.4282</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1111</v>
+        <v>-1.7413</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2651</v>
+        <v>-1.9456</v>
       </c>
       <c r="O2" t="n">
-        <v>0.154</v>
+        <v>0.2042</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7225</v>
+        <v>-0.5052</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3293</v>
+        <v>-0.6286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3932</v>
+        <v>0.1235</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1418</v>
+        <v>1.8608</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5393</v>
+        <v>3.2477</v>
       </c>
       <c r="E3" t="n">
-        <v>1.054</v>
+        <v>2.176</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4853</v>
+        <v>1.0716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8113</v>
+        <v>0.5566</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1788</v>
+        <v>2.601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6325</v>
+        <v>-2.0444</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5526</v>
+        <v>1.7614</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1244</v>
+        <v>4.01</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4282</v>
+        <v>-2.2486</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7413</v>
+        <v>-1.2048</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9456</v>
+        <v>-1.4091</v>
       </c>
       <c r="O3" t="n">
         <v>0.2042</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2473</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2204</v>
+        <v>-0.3449</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.411</v>
+        <v>-0.1215</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1907</v>
+        <v>-0.2234</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8608</v>
+        <v>0.2525</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7886</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.535</v>
+        <v>2.7451</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7658</v>
+        <v>0.2885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7692</v>
+        <v>2.4565</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5566</v>
+        <v>0.0709</v>
       </c>
       <c r="H4" t="n">
-        <v>2.601</v>
+        <v>0.7033</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0444</v>
+        <v>-0.6323</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7614</v>
+        <v>0.182</v>
       </c>
       <c r="K4" t="n">
-        <v>4.01</v>
+        <v>0.9683</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2486</v>
+        <v>-0.7863</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2048</v>
+        <v>-0.1111</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4091</v>
+        <v>-0.2651</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2042</v>
+        <v>0.154</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7834</v>
+        <v>2.5515</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0576</v>
+        <v>0.2645</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4683</v>
+        <v>0.1065</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5258</v>
+        <v>0.1579</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2525</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0069</v>
+        <v>1.2258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9314</v>
+        <v>-0.4074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0755</v>
+        <v>1.6332</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7447</v>
+        <v>1.0383</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3193</v>
+        <v>0.5162</v>
       </c>
       <c r="I5" t="n">
-        <v>1.064</v>
+        <v>0.5221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9235</v>
+        <v>0.7597</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0168</v>
+        <v>0.7597</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9067</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1788</v>
+        <v>0.2785</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3361</v>
+        <v>-0.2435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>0.5221</v>
       </c>
       <c r="P5" t="n">
         <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0303</v>
+        <v>0.3499</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.1491</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0224</v>
+        <v>0.4991</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4269</v>
+        <v>1.0405</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0718</v>
+        <v>0.9314</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4988</v>
+        <v>0.1091</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0383</v>
+        <v>0.7447</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5162</v>
+        <v>-0.3193</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5221</v>
+        <v>1.064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7597</v>
+        <v>0.9235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7597</v>
+        <v>0.0168</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.9067</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2785</v>
+        <v>-0.1788</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2435</v>
+        <v>-0.3361</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5221</v>
+        <v>0.1573</v>
       </c>
       <c r="P6" t="n">
         <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.449</v>
+        <v>0.0639</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8136</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3646</v>
+        <v>0.056</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3959</v>
+        <v>-0.2108</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0211</v>
+        <v>0.0969</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3749</v>
+        <v>-0.3076</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4613</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1871</v>
+        <v>-0.002</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
         <v>0.2525</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7755</v>
+        <v>-0.5322</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3693</v>
+        <v>-1.0587</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5937</v>
+        <v>0.5265</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0581</v>
@@ -1078,13 +1078,13 @@
         <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7328</v>
+        <v>-0.4894</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6484</v>
+        <v>-0.3378</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0843</v>
+        <v>-0.1516</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6257</v>
+        <v>-1.8115</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2996</v>
+        <v>-0.6534</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3261</v>
+        <v>-1.1581</v>
       </c>
       <c r="G9" t="n">
         <v>-1.393</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1436</v>
+        <v>-0.0422</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>-0.0077</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9911</v>
+        <v>-1.8524</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="F10" t="n">
+        <v>-1.0656</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.0452</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.366</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.6792</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.5079</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.6758999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.5373</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.534</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.3587</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.279</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.07969999999999999</v>
+      </c>
+      <c r="V10" t="n">
         <v>-1.0722</v>
       </c>
-      <c r="G10" t="n">
-        <v>-1.6845</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.1056</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.5788</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.7695</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.7695</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.9149</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.3361</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.5788</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.3066</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.1494</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.1573</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3982</v>
+        <v>-1.9911</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0974</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3008</v>
+        <v>-1.0722</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0452</v>
+        <v>-1.6845</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.366</v>
+        <v>-1.1056</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6792</v>
+        <v>-0.5788</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5079</v>
+        <v>-0.7695</v>
       </c>
       <c r="K11" t="n">
-        <v>0.168</v>
+        <v>-0.7695</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5373</v>
+        <v>-0.9149</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.534</v>
+        <v>-0.3361</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0033</v>
+        <v>-0.5788</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9045</v>
+        <v>-0.3066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.315</v>
+        <v>-0.1573</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4963</v>
+        <v>-3.0739</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4518</v>
+        <v>-2.6261</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0445</v>
+        <v>-0.4478</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7911</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1511</v>
+        <v>0.2713</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3364</v>
+        <v>-0.5107</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1852</v>
+        <v>0.782</v>
       </c>
       <c r="V12" t="n">
         <v>0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2748</v>
+        <v>-4.9146</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6998</v>
+        <v>-6.1716</v>
       </c>
       <c r="F13" t="n">
-        <v>1.425</v>
+        <v>1.257</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3305</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2851</v>
+        <v>-0.3547</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2794</v>
+        <v>-0.1924</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0057</v>
+        <v>-0.1623</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.246299999999999</v>
+        <v>-1.8729</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.667199999999999</v>
+        <v>-7.293699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.420800000000001</v>
+        <v>5.420700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-10.5419</v>
@@ -1516,13 +1516,13 @@
         <v>-4.5024</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.0394</v>
+        <v>-6.039400000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.166499999999999</v>
+        <v>0.1664999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1733</v>
+        <v>6.173299999999998</v>
       </c>
       <c r="L14" t="n">
         <v>-6.0068</v>
@@ -1534,7 +1534,7 @@
         <v>-10.6759</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.03269999999999994</v>
+        <v>-0.03269999999999992</v>
       </c>
       <c r="P14" t="n">
         <v>10.438</v>
@@ -1546,13 +1546,13 @@
         <v>19.7161</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8276</v>
+        <v>-1.4541</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5919</v>
+        <v>-2.2185</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7644</v>
+        <v>0.7645000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3147000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8363</v>
+        <v>7.1128</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1388</v>
+        <v>6.7286</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6974</v>
+        <v>0.3842</v>
       </c>
       <c r="G15" t="n">
         <v>3.5915</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2601</v>
+        <v>0.5366</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.955</v>
+        <v>-0.3653</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2151</v>
+        <v>0.9019</v>
       </c>
       <c r="V15" t="n">
         <v>3.2166</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5027</v>
+        <v>3.6227</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5133</v>
+        <v>-0.1595</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0161</v>
+        <v>3.7821</v>
       </c>
       <c r="G16" t="n">
         <v>2.7745</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0504</v>
+        <v>1.1703</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3655</v>
+        <v>-0.0116</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4159</v>
+        <v>1.1819</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2853</v>
+        <v>2.5656</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0698</v>
+        <v>-0.1661</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2155</v>
+        <v>2.7317</v>
       </c>
       <c r="G17" t="n">
         <v>2.0709</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0149</v>
+        <v>0.2653</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2785</v>
+        <v>0.2377</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1652</v>
+        <v>2.4956</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2374</v>
+        <v>0.8835</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9278999999999999</v>
+        <v>1.6121</v>
       </c>
       <c r="G18" t="n">
         <v>2.4699</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.105</v>
+        <v>0.4353</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6449</v>
+        <v>0.291</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5399</v>
+        <v>0.1443</v>
       </c>
       <c r="V18" t="n">
         <v>1.214</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9686</v>
+        <v>0.8698</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8502</v>
+        <v>-0.9257</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8817</v>
+        <v>1.7955</v>
       </c>
       <c r="G19" t="n">
-        <v>5.78</v>
+        <v>2.1598</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6552</v>
+        <v>0.2727</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1248</v>
+        <v>1.8871</v>
       </c>
       <c r="J19" t="n">
-        <v>6.5852</v>
+        <v>1.1808</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2971</v>
+        <v>-0.0805</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2882</v>
+        <v>1.2613</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8052</v>
+        <v>0.979</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6418</v>
+        <v>0.3532</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8366</v>
+        <v>0.6258</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.7112</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.871</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1549</v>
+        <v>0.0501</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2467</v>
+        <v>0.1614</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1114</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2551</v>
+        <v>0.2836</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1107</v>
+        <v>0.2836</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3035</v>
+        <v>0.316</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8077</v>
+        <v>1.6707</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1113</v>
+        <v>-1.3547</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1598</v>
+        <v>5.78</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2727</v>
+        <v>3.6552</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8871</v>
+        <v>2.1248</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1808</v>
+        <v>6.5852</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0805</v>
+        <v>5.2971</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2613</v>
+        <v>1.2882</v>
       </c>
       <c r="M20" t="n">
-        <v>0.979</v>
+        <v>-0.8052</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3532</v>
+        <v>-1.6418</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6258</v>
+        <v>0.8366</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6237</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-4.871</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5162</v>
+        <v>0.5023</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2794</v>
+        <v>0.0672</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7956</v>
+        <v>0.4351</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2836</v>
+        <v>-2.2551</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>-0.1107</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6192</v>
+        <v>-0.5057</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1321</v>
+        <v>-3.8962</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5129</v>
+        <v>3.3906</v>
       </c>
       <c r="G21" t="n">
         <v>1.4285</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3413</v>
+        <v>0.4549</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7894</v>
+        <v>0.6671</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1034</v>
+        <v>-1.7953</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4271</v>
+        <v>-1.5451</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6763</v>
+        <v>-0.2502</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1491</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1863</v>
+        <v>0.1219</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0018</v>
+        <v>0.4244</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6068</v>
+        <v>-4.3373</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7712</v>
+        <v>-1.5353</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8355</v>
+        <v>-2.8019</v>
       </c>
       <c r="G23" t="n">
         <v>-3.887</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0303</v>
+        <v>0.2998</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4705</v>
+        <v>0.5041</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4859</v>
+        <v>-5.7389</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.3876</v>
+        <v>-5.7978</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0983</v>
+        <v>0.0589</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6971</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3971</v>
+        <v>0.3499</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8057</v>
+        <v>-0.2159</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4086</v>
+        <v>0.5658</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.246299999999999</v>
+        <v>4.605300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.742800000000001</v>
+        <v>-4.742900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>6.9893</v>
+        <v>9.3483</v>
       </c>
       <c r="G25" t="n">
         <v>10.5419</v>
@@ -2404,13 +2404,13 @@
         <v>9.278300000000002</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8275</v>
+        <v>4.1864</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7644</v>
+        <v>-0.7645</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5919</v>
+        <v>4.950900000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.3146999999999998</v>
